--- a/docs/observability/Token_Savings_Log.xlsx
+++ b/docs/observability/Token_Savings_Log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -741,94 +741,573 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14:10:35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15:10:35</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>77500</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>14:10:54</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>15:10:54</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>77500</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14:23:00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15:23:00</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>79050</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
           <t>13:35:00</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>15:30:00</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E9" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F9" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G9" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H9" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I9" s="6" t="n">
         <v>26800</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K9" s="6" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15:05:12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16:05:12</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>98150</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>15:20:08</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>16:20:08</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>291</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>291</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>105550</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>15:22:34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16:22:34</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>105800</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>15:23:07</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>16:23:07</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>293</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>293</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>106050</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15:28:56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16:28:56</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>110900</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>15:34:53</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>16:34:53</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>307</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>307</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>111150</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>2026-04-28 TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="n">
-        <v>320</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>313</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>103050</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="n">
+        <v>860</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2618</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2718</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>974700</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>03:18:18</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>04:18:18</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="n">
-        <v>980</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>333</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>340</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>109500</v>
-      </c>
-      <c r="J8" s="7" t="inlineStr"/>
-      <c r="K8" s="7" t="n">
-        <v>29</v>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="7" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2740</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2747</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>372</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>982450</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="n">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -842,7 +1321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -905,38 +1384,57 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5.33</v>
+        <v>14.33</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>213</v>
+        <v>2618</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>103050</v>
+        <v>974700</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="7">
-        <f>SUM(B2:B3)</f>
+      <c r="B5" s="7">
+        <f>SUM(B2:B4)</f>
         <v/>
       </c>
-      <c r="C4" s="7">
-        <f>SUM(C2:C3)</f>
+      <c r="C5" s="7">
+        <f>SUM(C2:C4)</f>
         <v/>
       </c>
-      <c r="D4" s="7">
-        <f>SUM(D2:D3)</f>
+      <c r="D5" s="7">
+        <f>SUM(D2:D4)</f>
         <v/>
       </c>
-      <c r="E4" s="7">
-        <f>SUM(E2:E3)</f>
+      <c r="E5" s="7">
+        <f>SUM(E2:E4)</f>
         <v/>
       </c>
     </row>
@@ -995,16 +1493,16 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>16.33</v>
+        <v>26.33</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>109500</v>
+        <v>982450</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6705</v>
+        <v>37313</v>
       </c>
     </row>
     <row r="3">

--- a/docs/observability/Token_Savings_Log.xlsx
+++ b/docs/observability/Token_Savings_Log.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -741,28 +741,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14:10:35</t>
+          <t>13:35:00</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15:10:35</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>77500</v>
+        <v>26800</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -770,58 +770,42 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>14:10:54</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>15:10:54</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>214</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>214</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>77500</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>11</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-28 TOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>103050</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -831,28 +815,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14:23:00</t>
+          <t>04:12:45</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15:23:00</t>
+          <t>05:12:45</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
         <v>60</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>217</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>79050</v>
+        <v>29300</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -860,454 +844,65 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>13:35:00</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>15:30:00</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>26800</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>4</v>
+      <c r="I9" s="4" t="n">
+        <v>29300</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>15:05:12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16:05:12</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>98150</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>15:20:08</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>16:20:08</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>291</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>291</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>105550</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15:22:34</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16:22:34</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>105800</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>15:23:07</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>16:23:07</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>293</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>293</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>106050</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>15:28:56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>16:28:56</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>110900</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>15:34:53</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>16:34:53</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>307</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>307</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>111150</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-28 TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="n">
-        <v>860</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>2618</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2718</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>369</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>974700</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>03:18:18</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>04:18:18</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-29 TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr"/>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="n">
-        <v>1580</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>2740</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>2747</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>372</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>982450</v>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" s="7" t="n">
-        <v>157</v>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>415</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>422</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>138800</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1384,16 +979,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>14.33</v>
+        <v>5.33</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2618</v>
+        <v>213</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>974700</v>
+        <v>103050</v>
       </c>
     </row>
     <row r="4">
@@ -1409,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1300</v>
+        <v>29300</v>
       </c>
     </row>
     <row r="5">
@@ -1493,16 +1088,16 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>26.33</v>
+        <v>17.33</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>982450</v>
+        <v>138800</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>37313</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="3">
